--- a/abcdf.xlsx
+++ b/abcdf.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,21 +504,6 @@
           <t>unit_price</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>tax_type</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>tax_rate</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>tax_amount</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -526,47 +511,49 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MA109305</t>
+          <t>126757</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>KRAMW01 1202206039672</t>
-        </is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>123456789</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sanpac Africa Ltd</t>
+          <t>INDUSTRIAL SUPPLIERS LTD.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>P O Box 20496 - 00200 Nairobi, Kenya
-P O Box 87025 - 80100 Mombasa, Kenya</t>
+          <t>AGA KHAN
+ROAD
+NEAR BLOOD CENTRE
+P. O. Box 97044 - 80112, MOMBASA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tel: +254 (0)20 2112100/1/2/3
-Cell : +254 (0)733 201 338, (0)722 201 338, (0)756 201 338
-Email: sansales @ sanpac.com</t>
+          <t>Tel : 041 2314147, 041 2223422
+: 041 2314518, 041 2315013
+Mobile : 0723 338476, 0735 338478
+: 0794 895749/50, 0731 768851
+E-mail . : info@jalaramkenya.com</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>24002984</t>
+          <t>24004829</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>568980</v>
+        <v>10200</v>
       </c>
       <c r="J2" t="n">
-        <v>660016.8</v>
+        <v>11832</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -574,188 +561,23 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>91036.8</v>
+        <v>1632</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>P0005943160 x</t>
+          <t>P 051107439 Y</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Round Jerryean Yellow 10ltr</t>
+          <t>Black Gasket Maker</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>4360</v>
+        <v>60</v>
       </c>
       <c r="P2" t="n">
-        <v>118.8</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MA109305</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>KRAMW01 1202206039672</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Sanpac Africa Ltd</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>P O Box 20496 - 00200 Nairobi, Kenya
-P O Box 87025 - 80100 Mombasa, Kenya</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Tel: +254 (0)20 2112100/1/2/3
-Cell : +254 (0)733 201 338, (0)722 201 338, (0)756 201 338
-Email: sansales @ sanpac.com</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>24002984</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>568980</v>
-      </c>
-      <c r="J3" t="n">
-        <v>660016.8</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>KES</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>91036.8</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>P0005943160 x</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Bung Cap &amp; Gasket Sky Blue</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>4360</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>MA109305</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>KRAMW01 1202206039672</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Sanpac Africa Ltd</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>P O Box 20496 - 00200 Nairobi, Kenya
-P O Box 87025 - 80100 Mombasa, Kenya</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Tel: +254 (0)20 2112100/1/2/3
-Cell : +254 (0)733 201 338, (0)722 201 338, (0)756 201 338
-Email: sansales @ sanpac.com</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>24002984</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>568980</v>
-      </c>
-      <c r="J4" t="n">
-        <v>660016.8</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>KES</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>91036.8</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>P0005943160 x</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Woven Bags for 10ltr</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>436</v>
-      </c>
-      <c r="P4" t="n">
-        <v>64</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>VAT</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>16%</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>91036.8</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/abcdf.xlsx
+++ b/abcdf.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,17 +491,32 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>vat_pin</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>unit_price</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>received on</t>
         </is>
       </c>
     </row>
@@ -511,49 +526,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>126757</t>
+          <t>120667</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>123456789</v>
-      </c>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>INDUSTRIAL SUPPLIERS LTD.</t>
+          <t>KOBIAN KENYA LIMITED</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AGA KHAN
-ROAD
-NEAR BLOOD CENTRE
-P. O. Box 97044 - 80112, MOMBASA</t>
+          <t>KOBIAN HOUSE,MOMBASA ROAD
+P.O. BOX 46617- NAIROBI 00100 GPO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tel : 041 2314147, 041 2223422
-: 041 2314518, 041 2315013
-Mobile : 0723 338476, 0735 338478
-: 0794 895749/50, 0731 768851
-E-mail . : info@jalaramkenya.com</t>
+          <t>Office Line:0202161265/6
+Cell Phone: 0723888006 0786888006
+sales@kobianscientific.com</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>24004829</t>
+          <t>24001844</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>10200</v>
+        <v>31000</v>
       </c>
       <c r="J2" t="n">
-        <v>11832</v>
+        <v>35960</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -561,23 +570,458 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1632</v>
+        <v>4960</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>P 051107439 Y</t>
+          <t>P051092185B</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Black Gasket Maker</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>60</v>
+          <t>P0006118530</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Petroleum Spirit ACS Reagent,40-60°C,90+%-2.5L</t>
+        </is>
       </c>
       <c r="P2" t="n">
-        <v>170</v>
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3450</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Not Provided</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Vendor Portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>120667</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>KOBIAN KENYA LIMITED</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>KOBIAN HOUSE,MOMBASA ROAD
+P.O. BOX 46617- NAIROBI 00100 GPO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Office Line:0202161265/6
+Cell Phone: 0723888006 0786888006
+sales@kobianscientific.com</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>24001844</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>31000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>35960</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>KES</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>4960</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>P051092185B</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>P0006118530</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Acetic Acid Glacial Extra Pure,99.5%-2.5L</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2100</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Not Provided</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Vendor Portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>120667</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>KOBIAN KENYA LIMITED</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KOBIAN HOUSE,MOMBASA ROAD
+P.O. BOX 46617- NAIROBI 00100 GPO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Office Line:0202161265/6
+Cell Phone: 0723888006 0786888006
+sales@kobianscientific.com</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>24001844</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>31000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>35960</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>KES</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>4960</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>P051092185B</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>P0006118530</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2,2,4-Trimethylpentane(Isooctane),99.5+%(GC)-2.5L</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Not Provided</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Vendor Portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>120667</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>KOBIAN KENYA LIMITED</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>KOBIAN HOUSE,MOMBASA ROAD
+P.O. BOX 46617- NAIROBI 00100 GPO</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Office Line:0202161265/6
+Cell Phone: 0723888006 0786888006
+sales@kobianscientific.com</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>24001844</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>31000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>35960</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>KES</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>4960</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>P051092185B</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>P0006118530</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Acetone Puriss.p.a.,ACS Reagent,99.5+%(GC)-2.5L</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Not Provided</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Vendor Portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>120667</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>KOBIAN KENYA LIMITED</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>KOBIAN HOUSE,MOMBASA ROAD
+P.O. BOX 46617- NAIROBI 00100 GPO</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Office Line:0202161265/6
+Cell Phone: 0723888006 0786888006
+sales@kobianscientific.com</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>24001844</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>31000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>35960</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>KES</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>4960</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>P051092185B</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>P0006118530</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Hydrochloric Acid Extra Pure,35%-2.5L</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Not Provided</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Vendor Portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>120667</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>KOBIAN KENYA LIMITED</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KOBIAN HOUSE,MOMBASA ROAD
+P.O. BOX 46617- NAIROBI 00100 GPO</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Office Line:0202161265/6
+Cell Phone: 0723888006 0786888006
+sales@kobianscientific.com</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>24001844</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>31000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>35960</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>KES</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>4960</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>P051092185B</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>P0006118530</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Sulphuric Acid Extra Pure,98%-2.5L</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Not Provided</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Vendor Portal</t>
+        </is>
       </c>
     </row>
   </sheetData>
